--- a/artfynd/A 58154-2023 artfynd.xlsx
+++ b/artfynd/A 58154-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58154-2023 artfynd.xlsx
+++ b/artfynd/A 58154-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66499404</v>
+        <v>66499419</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444004.2778370188</v>
+        <v>444005</v>
       </c>
       <c r="R2" t="n">
-        <v>6901994.323229411</v>
+        <v>6902146</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66499422</v>
+        <v>66499421</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,38 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Morsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444002.9872883423</v>
+        <v>444003</v>
       </c>
       <c r="R3" t="n">
-        <v>6902169.13681573</v>
+        <v>6902169</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,21 +845,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -895,7 +861,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>12646</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66499401</v>
+        <v>66499406</v>
       </c>
       <c r="B4" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -957,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443981.7231429141</v>
+        <v>444004</v>
       </c>
       <c r="R4" t="n">
-        <v>6901957.408659218</v>
+        <v>6901994</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -990,21 +951,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1016,7 +967,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1034,15 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66499405</v>
+        <v>66499407</v>
       </c>
       <c r="B5" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,38 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Morsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444004.2778370188</v>
+        <v>443981</v>
       </c>
       <c r="R5" t="n">
-        <v>6901994.323229411</v>
+        <v>6902037</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1111,21 +1053,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1137,7 +1069,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>12634</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1155,15 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66499408</v>
+        <v>66499424</v>
       </c>
       <c r="B6" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1195,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443980.7169846953</v>
+        <v>444003</v>
       </c>
       <c r="R6" t="n">
-        <v>6902037.132629314</v>
+        <v>6902169</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1228,21 +1155,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1254,7 +1171,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1272,37 +1189,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66499403</v>
+        <v>66499409</v>
       </c>
       <c r="B7" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1312,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443975.3138010828</v>
+        <v>443981</v>
       </c>
       <c r="R7" t="n">
-        <v>6901964.97348043</v>
+        <v>6902037</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1345,21 +1257,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1371,7 +1273,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,37 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66499419</v>
+        <v>66499396</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444005.4070458606</v>
+        <v>443988</v>
       </c>
       <c r="R8" t="n">
-        <v>6902146.257539982</v>
+        <v>6901940</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1462,21 +1359,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1488,7 +1375,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1506,15 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66499396</v>
+        <v>66499404</v>
       </c>
       <c r="B9" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443987.9695422066</v>
+        <v>444004</v>
       </c>
       <c r="R9" t="n">
-        <v>6901940.057791995</v>
+        <v>6901994</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1579,21 +1461,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1605,7 +1477,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1626,12 +1498,7 @@
         <v>66499418</v>
       </c>
       <c r="B10" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,12 +1515,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444000.6097155453</v>
+        <v>444001</v>
       </c>
       <c r="R10" t="n">
-        <v>6902110.4472675</v>
+        <v>6902110</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1696,19 +1563,9 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2011-08-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,15 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66499416</v>
+        <v>66499397</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,34 +1608,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Morsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444000.6097155453</v>
+        <v>443988</v>
       </c>
       <c r="R11" t="n">
-        <v>6902110.4472675</v>
+        <v>6901940</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1813,21 +1669,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1839,7 +1685,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1857,15 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66499421</v>
+        <v>66499401</v>
       </c>
       <c r="B12" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,34 +1714,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Morsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444002.9872883423</v>
+        <v>443982</v>
       </c>
       <c r="R12" t="n">
-        <v>6902169.13681573</v>
+        <v>6901957</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1930,21 +1775,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1956,7 +1791,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>12646</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1974,50 +1809,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66499411</v>
+        <v>66499405</v>
       </c>
       <c r="B13" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Morsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443989.9241337917</v>
+        <v>444004</v>
       </c>
       <c r="R13" t="n">
-        <v>6902085.455263146</v>
+        <v>6901994</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2047,21 +1881,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2073,7 +1897,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>12638</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2091,15 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66499406</v>
+        <v>66499408</v>
       </c>
       <c r="B14" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,38 +1926,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Morsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444004.2778370188</v>
+        <v>443981</v>
       </c>
       <c r="R14" t="n">
-        <v>6901994.323229411</v>
+        <v>6902037</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2168,21 +1983,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +1999,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2212,15 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66499397</v>
+        <v>66499413</v>
       </c>
       <c r="B15" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,38 +2028,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Morsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443987.9695422066</v>
+        <v>443990</v>
       </c>
       <c r="R15" t="n">
-        <v>6901940.057791995</v>
+        <v>6902085</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2289,21 +2085,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2315,7 +2101,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2333,15 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66499409</v>
+        <v>66499416</v>
       </c>
       <c r="B16" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2349,21 +2130,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2373,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443980.7169846953</v>
+        <v>444001</v>
       </c>
       <c r="R16" t="n">
-        <v>6902037.132629314</v>
+        <v>6902110</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2406,21 +2187,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2432,7 +2203,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2450,50 +2221,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66499398</v>
+        <v>66499422</v>
       </c>
       <c r="B17" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Morsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443981.7231429141</v>
+        <v>444003</v>
       </c>
       <c r="R17" t="n">
-        <v>6901957.408659218</v>
+        <v>6902169</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2523,21 +2293,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2549,7 +2309,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2567,15 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66499424</v>
+        <v>66499403</v>
       </c>
       <c r="B18" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2607,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444002.9872883423</v>
+        <v>443975</v>
       </c>
       <c r="R18" t="n">
-        <v>6902169.13681573</v>
+        <v>6901965</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2640,21 +2395,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2666,7 +2411,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>12630</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2684,15 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66499402</v>
+        <v>66499398</v>
       </c>
       <c r="B19" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2724,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443975.3138010828</v>
+        <v>443982</v>
       </c>
       <c r="R19" t="n">
-        <v>6901964.97348043</v>
+        <v>6901957</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2757,21 +2497,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2783,7 +2513,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>12626</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2801,15 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66499407</v>
+        <v>66499410</v>
       </c>
       <c r="B20" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2841,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443980.7169846953</v>
+        <v>443990</v>
       </c>
       <c r="R20" t="n">
-        <v>6902037.132629314</v>
+        <v>6902085</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2874,21 +2599,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2900,7 +2615,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>12637</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2921,12 +2636,7 @@
         <v>66499414</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2958,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444000.6097155453</v>
+        <v>444001</v>
       </c>
       <c r="R21" t="n">
-        <v>6902110.4472675</v>
+        <v>6902110</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2991,19 +2701,9 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2011-08-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3035,37 +2735,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>66499399</v>
+        <v>66499417</v>
       </c>
       <c r="B22" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6459</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3075,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443981.7231429141</v>
+        <v>444001</v>
       </c>
       <c r="R22" t="n">
-        <v>6901957.408659218</v>
+        <v>6902110</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3108,21 +2803,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3134,7 +2819,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3152,37 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66499413</v>
+        <v>66499411</v>
       </c>
       <c r="B23" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3192,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443989.9241337917</v>
+        <v>443990</v>
       </c>
       <c r="R23" t="n">
-        <v>6902085.455263146</v>
+        <v>6902085</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3225,21 +2905,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3251,7 +2921,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12638</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3269,15 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>66499410</v>
+        <v>66499402</v>
       </c>
       <c r="B24" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,21 +2950,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3309,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443989.9241337917</v>
+        <v>443975</v>
       </c>
       <c r="R24" t="n">
-        <v>6902085.455263146</v>
+        <v>6901965</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3342,21 +3007,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3368,7 +3023,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3386,37 +3041,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>66499415</v>
+        <v>66499399</v>
       </c>
       <c r="B25" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3426,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444000.6097155453</v>
+        <v>443982</v>
       </c>
       <c r="R25" t="n">
-        <v>6902110.4472675</v>
+        <v>6901957</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3459,21 +3109,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3485,7 +3125,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3503,15 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>66499417</v>
+        <v>66499415</v>
       </c>
       <c r="B26" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,21 +3154,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6459</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3543,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444000.6097155453</v>
+        <v>444001</v>
       </c>
       <c r="R26" t="n">
-        <v>6902110.4472675</v>
+        <v>6902110</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3576,21 +3211,11 @@
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2011-08-12</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3602,7 +3227,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 58154-2023 artfynd.xlsx
+++ b/artfynd/A 58154-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499419</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499406</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499407</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499424</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499409</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499396</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499404</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499418</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499397</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499401</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499405</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499408</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499413</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499416</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2324,6 +2404,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499422</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2426,6 +2511,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499403</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2528,6 +2618,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499398</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2630,6 +2725,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499410</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2732,6 +2832,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499414</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2834,6 +2939,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499417</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2936,6 +3046,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499411</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3038,6 +3153,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499402</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3140,6 +3260,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499399</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3242,8 +3367,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499415</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>